--- a/data/Basketball_Analytics_2025-2026.xlsx
+++ b/data/Basketball_Analytics_2025-2026.xlsx
@@ -10576,8 +10576,14 @@
           <t>Israel</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2000-02-20</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>1.88</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -10594,66 +10600,86 @@
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>1997-11-05</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>1.91</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>24783</v>
+        <v>21818</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Yarin</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Sela</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
+          <t>Hasson</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2004-10-10</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>2.08</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>21818</v>
+        <v>21869</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Yarin</t>
+          <t>Kalib</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Hasson</t>
+          <t>Boone</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2000-11-30</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>2.02</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>21869</v>
+        <v>24783</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Kalib</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Boone</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Sela</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="n">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -10675,7 +10701,9 @@
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" t="n">
+        <v>1.93</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -10697,7 +10725,9 @@
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" t="n">
+        <v>1.94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10710,7 +10740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,6 +17317,123 @@
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>21821</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>7</v>
+      </c>
+      <c r="E356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>22777</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>24783</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="n">
+        <v>8</v>
+      </c>
+      <c r="E358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>21818</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>36</v>
+      </c>
+      <c r="E359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>21869</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>24778</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="n">
+        <v>11</v>
+      </c>
+      <c r="E361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>24796</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="n">
+        <v>30</v>
+      </c>
+      <c r="E362" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17553,16 +17700,16 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5496</v>
+        <v>5516</v>
       </c>
       <c r="D4" t="n">
-        <v>2258</v>
+        <v>2265</v>
       </c>
       <c r="E4" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F4" t="n">
-        <v>1787</v>
+        <v>1794</v>
       </c>
       <c r="G4" t="n">
         <v>45.7</v>
@@ -17571,16 +17718,16 @@
         <v>243</v>
       </c>
       <c r="I4" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="J4" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="K4" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L4" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M4" t="n">
         <v>71.2</v>
@@ -17589,13 +17736,13 @@
         <v>211</v>
       </c>
       <c r="O4" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="P4" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="Q4" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="R4" t="n">
         <v>359</v>
@@ -17604,10 +17751,10 @@
         <v>172</v>
       </c>
       <c r="T4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>2337</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="5">
@@ -17754,7 +17901,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>5244</v>
+        <v>5250</v>
       </c>
       <c r="D7" t="n">
         <v>2236</v>
@@ -17763,16 +17910,16 @@
         <v>831</v>
       </c>
       <c r="F7" t="n">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="G7" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="H7" t="n">
         <v>256</v>
       </c>
       <c r="I7" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J7" t="n">
         <v>33.3</v>
@@ -17808,7 +17955,7 @@
         <v>99</v>
       </c>
       <c r="U7" t="n">
-        <v>2188</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="8">
@@ -17955,61 +18102,61 @@
         <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>6217</v>
+        <v>6279</v>
       </c>
       <c r="D10" t="n">
-        <v>2355</v>
+        <v>2372</v>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="F10" t="n">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="G10" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
       </c>
       <c r="I10" t="n">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="J10" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="K10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L10" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M10" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O10" t="n">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="P10" t="n">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="Q10" t="n">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="R10" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="S10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="T10" t="n">
         <v>62</v>
       </c>
       <c r="U10" t="n">
-        <v>2346</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="11">
@@ -18290,61 +18437,61 @@
         <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>5682</v>
+        <v>6107</v>
       </c>
       <c r="D15" t="n">
-        <v>2337</v>
+        <v>2466</v>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>950</v>
       </c>
       <c r="F15" t="n">
-        <v>1934</v>
+        <v>2057</v>
       </c>
       <c r="G15" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="H15" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I15" t="n">
-        <v>559</v>
+        <v>602</v>
       </c>
       <c r="J15" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="K15" t="n">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="L15" t="n">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="M15" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="O15" t="n">
-        <v>713</v>
+        <v>750</v>
       </c>
       <c r="P15" t="n">
-        <v>1052</v>
+        <v>1107</v>
       </c>
       <c r="Q15" t="n">
-        <v>493</v>
+        <v>557</v>
       </c>
       <c r="R15" t="n">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="S15" t="n">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="T15" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U15" t="n">
-        <v>2478</v>
+        <v>2591</v>
       </c>
     </row>
   </sheetData>
